--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_3_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_3_bus.xlsx
@@ -720,22 +720,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100337922457805</v>
+        <v>1.100337922457813</v>
       </c>
       <c r="O2">
-        <v>1.098746913077538</v>
+        <v>1.098746913077529</v>
       </c>
       <c r="P2">
-        <v>1.099035451920491</v>
+        <v>1.099035451920474</v>
       </c>
       <c r="Q2">
         <v>29.95214969133516</v>
       </c>
       <c r="R2">
-        <v>-90.07840407750486</v>
+        <v>-90.07840407750587</v>
       </c>
       <c r="S2">
-        <v>150.0087152761925</v>
+        <v>150.0087152761928</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.974925303142463</v>
+        <v>0.9749253031449129</v>
       </c>
       <c r="O3">
-        <v>0.4120301105219046</v>
+        <v>0.4120301105145847</v>
       </c>
       <c r="P3">
-        <v>0.9743742289074824</v>
+        <v>0.9743742289070986</v>
       </c>
       <c r="Q3">
-        <v>12.19933686481243</v>
+        <v>12.19933686472099</v>
       </c>
       <c r="R3">
-        <v>-90.07840236731998</v>
+        <v>-90.07840236756461</v>
       </c>
       <c r="S3">
-        <v>167.7936573080316</v>
+        <v>167.7936573084069</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9749252976995502</v>
+        <v>0.9749252977014852</v>
       </c>
       <c r="O4">
-        <v>0.412030134678999</v>
+        <v>0.4120301346708266</v>
       </c>
       <c r="P4">
-        <v>0.9743742394610851</v>
+        <v>0.9743742394586994</v>
       </c>
       <c r="Q4">
-        <v>12.19933766089119</v>
+        <v>12.19933766075253</v>
       </c>
       <c r="R4">
-        <v>-90.07840008707321</v>
+        <v>-90.07840008755761</v>
       </c>
       <c r="S4">
-        <v>167.7936567149244</v>
+        <v>167.7936567152719</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -864,55 +864,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.222491890803654</v>
+        <v>0.2224918908036303</v>
       </c>
       <c r="D5">
-        <v>0.222491890803654</v>
+        <v>0.2224918908036302</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.05138230198485533</v>
+        <v>0.05138230198484986</v>
       </c>
       <c r="G5">
-        <v>0.05138230198485535</v>
+        <v>0.05138230198484985</v>
       </c>
       <c r="H5">
-        <v>2.355710883899123</v>
+        <v>2.048813925111795</v>
       </c>
       <c r="I5">
-        <v>1.590737958073062</v>
+        <v>1.383395955732901</v>
       </c>
       <c r="J5">
-        <v>0.8185751075880874</v>
+        <v>0.818575107564779</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339436</v>
+        <v>0.5546714956012828</v>
       </c>
       <c r="L5">
-        <v>0.8185751075880753</v>
+        <v>0.8185751075552288</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339499</v>
+        <v>0.5546714956491662</v>
       </c>
       <c r="N5">
-        <v>0.9526279648105385</v>
+        <v>0.9526279648124909</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279648105336</v>
+        <v>0.9526279648096452</v>
       </c>
       <c r="Q5">
-        <v>3.421916416635075E-13</v>
+        <v>-8.918313808265531E-11</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999999924</v>
+        <v>-179.999999999442</v>
       </c>
     </row>
   </sheetData>
@@ -1025,22 +1025,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050039495132281</v>
+        <v>1.050039495132282</v>
       </c>
       <c r="O2">
-        <v>1.049707799194494</v>
+        <v>1.049707799194493</v>
       </c>
       <c r="P2">
-        <v>1.04981433611069</v>
+        <v>1.049814336110686</v>
       </c>
       <c r="Q2">
-        <v>29.98955001158253</v>
+        <v>29.98955001158254</v>
       </c>
       <c r="R2">
-        <v>-90.01419001072954</v>
+        <v>-90.01419001072979</v>
       </c>
       <c r="S2">
-        <v>150.0033579443353</v>
+        <v>150.0033579443352</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1084,22 +1084,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.006805793168573</v>
+        <v>1.006805793168834</v>
       </c>
       <c r="O3">
-        <v>0.9078605358284628</v>
+        <v>0.9078605358270047</v>
       </c>
       <c r="P3">
-        <v>1.025766699057775</v>
+        <v>1.025766699056649</v>
       </c>
       <c r="Q3">
-        <v>26.79110438557203</v>
+        <v>26.79110438556225</v>
       </c>
       <c r="R3">
-        <v>-88.66248654638244</v>
+        <v>-88.66248654643546</v>
       </c>
       <c r="S3">
-        <v>153.7424278024565</v>
+        <v>153.7424278025129</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1143,22 +1143,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.006805793233227</v>
+        <v>1.006805793233553</v>
       </c>
       <c r="O4">
-        <v>0.9078605413991157</v>
+        <v>0.9078605413976844</v>
       </c>
       <c r="P4">
-        <v>1.025766701459484</v>
+        <v>1.025766701458085</v>
       </c>
       <c r="Q4">
-        <v>26.79110455936923</v>
+        <v>26.7911045593537</v>
       </c>
       <c r="R4">
-        <v>-88.66248638808048</v>
+        <v>-88.66248638816239</v>
       </c>
       <c r="S4">
-        <v>153.7424276970259</v>
+        <v>153.7424276970686</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1169,55 +1169,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.04655939234957938</v>
+        <v>0.04655939234957741</v>
       </c>
       <c r="D5">
-        <v>0.04655939234957939</v>
+        <v>0.04655939234957739</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.01075243124275773</v>
+        <v>0.01075243124275728</v>
       </c>
       <c r="G5">
-        <v>0.01075243124275773</v>
+        <v>0.01075243124275727</v>
       </c>
       <c r="H5">
-        <v>2.355702822977616</v>
+        <v>2.048805864161414</v>
       </c>
       <c r="I5">
-        <v>1.590658300946586</v>
+        <v>1.383316298638611</v>
       </c>
       <c r="J5">
-        <v>0.8185671472787982</v>
+        <v>0.8185671472608929</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806581</v>
+        <v>0.5545918926652642</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788021</v>
+        <v>0.818567147237338</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806922</v>
+        <v>0.5545918926849845</v>
       </c>
       <c r="N5">
-        <v>0.9824760196566827</v>
+        <v>0.982476019656932</v>
       </c>
       <c r="O5">
-        <v>0.8230615391932473</v>
+        <v>0.8230615391910707</v>
       </c>
       <c r="P5">
-        <v>1.01351165224947</v>
+        <v>1.013511652247757</v>
       </c>
       <c r="Q5">
-        <v>24.74069273982064</v>
+        <v>24.74069273980258</v>
       </c>
       <c r="R5">
-        <v>-87.62817348964566</v>
+        <v>-87.62817348973466</v>
       </c>
       <c r="S5">
-        <v>156.0652141911277</v>
+        <v>156.065214191205</v>
       </c>
     </row>
   </sheetData>
@@ -1330,19 +1330,19 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100043420168866</v>
+        <v>1.100043420168869</v>
       </c>
       <c r="O2">
-        <v>1.09967938667933</v>
+        <v>1.099679386679329</v>
       </c>
       <c r="P2">
-        <v>1.09979631258021</v>
+        <v>1.099796312580207</v>
       </c>
       <c r="Q2">
-        <v>29.98905253111945</v>
+        <v>29.98905253111947</v>
       </c>
       <c r="R2">
-        <v>-90.01486552855616</v>
+        <v>-90.01486552855641</v>
       </c>
       <c r="S2">
         <v>150.0035179545644</v>
@@ -1389,22 +1389,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.054751351131307</v>
+        <v>1.054751351132026</v>
       </c>
       <c r="O3">
-        <v>0.951079450868936</v>
+        <v>0.9510794508674384</v>
       </c>
       <c r="P3">
-        <v>1.074604916654206</v>
+        <v>1.074604916653663</v>
       </c>
       <c r="Q3">
-        <v>26.79066441259839</v>
+        <v>26.79066441256872</v>
       </c>
       <c r="R3">
-        <v>-88.66316206408736</v>
+        <v>-88.66316206413617</v>
       </c>
       <c r="S3">
-        <v>153.7425870915138</v>
+        <v>153.7425870915777</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1448,22 +1448,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.05475135119874</v>
+        <v>1.054751351199358</v>
       </c>
       <c r="O4">
-        <v>0.9510794567050042</v>
+        <v>0.9510794567033587</v>
       </c>
       <c r="P4">
-        <v>1.074604919170626</v>
+        <v>1.074604919169689</v>
       </c>
       <c r="Q4">
-        <v>26.79066458640767</v>
+        <v>26.79066458637107</v>
       </c>
       <c r="R4">
-        <v>-88.66316190573735</v>
+        <v>-88.66316190581101</v>
       </c>
       <c r="S4">
-        <v>153.7425869860865</v>
+        <v>153.7425869861387</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1474,55 +1474,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.0487758632092391</v>
+        <v>0.04877586320923143</v>
       </c>
       <c r="D5">
-        <v>0.04877586320923909</v>
+        <v>0.04877586320923143</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.01126430326937542</v>
+        <v>0.01126430326937365</v>
       </c>
       <c r="G5">
-        <v>0.01126430326937542</v>
+        <v>0.01126430326937365</v>
       </c>
       <c r="H5">
-        <v>2.355710883899123</v>
+        <v>2.048813925111795</v>
       </c>
       <c r="I5">
-        <v>1.590737958073062</v>
+        <v>1.383395955732901</v>
       </c>
       <c r="J5">
-        <v>0.8185751075880874</v>
+        <v>0.818575107564779</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339436</v>
+        <v>0.5546714956012828</v>
       </c>
       <c r="L5">
-        <v>0.8185751075880753</v>
+        <v>0.8185751075552288</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339499</v>
+        <v>0.5546714956491662</v>
       </c>
       <c r="N5">
-        <v>1.029263187415904</v>
+        <v>1.02926318741661</v>
       </c>
       <c r="O5">
-        <v>0.8622435779885818</v>
+        <v>0.8622435779863501</v>
       </c>
       <c r="P5">
-        <v>1.06176709479992</v>
+        <v>1.061767094798785</v>
       </c>
       <c r="Q5">
-        <v>24.74029097070589</v>
+        <v>24.74029097066915</v>
       </c>
       <c r="R5">
-        <v>-87.62884900732172</v>
+        <v>-87.62884900740387</v>
       </c>
       <c r="S5">
-        <v>156.0653689880247</v>
+        <v>156.0653689881082</v>
       </c>
     </row>
   </sheetData>
@@ -1635,22 +1635,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9503094932530869</v>
+        <v>0.950309493253096</v>
       </c>
       <c r="O2">
-        <v>0.9495401076448401</v>
+        <v>0.9495401076448396</v>
       </c>
       <c r="P2">
-        <v>0.9494603946829356</v>
+        <v>0.9494603946829421</v>
       </c>
       <c r="Q2">
-        <v>29.97320412474804</v>
+        <v>29.97320412474827</v>
       </c>
       <c r="R2">
-        <v>-90.05915402191762</v>
+        <v>-90.05915402191727</v>
       </c>
       <c r="S2">
-        <v>149.9972403488329</v>
+        <v>149.9972403488337</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1694,22 +1694,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8419472893600802</v>
+        <v>0.8419472893650201</v>
       </c>
       <c r="O3">
-        <v>0.3560775704246564</v>
+        <v>0.3560775704275623</v>
       </c>
       <c r="P3">
-        <v>0.8415879906725757</v>
+        <v>0.8415879906802013</v>
       </c>
       <c r="Q3">
-        <v>12.20796166665683</v>
+        <v>12.20796166650289</v>
       </c>
       <c r="R3">
-        <v>-90.05915231104632</v>
+        <v>-90.05915231078612</v>
       </c>
       <c r="S3">
-        <v>167.7867460118634</v>
+        <v>167.786746011692</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1753,22 +1753,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8419472866911132</v>
+        <v>0.8419472866966821</v>
       </c>
       <c r="O4">
-        <v>0.3560776105017723</v>
+        <v>0.3560776105071985</v>
       </c>
       <c r="P4">
-        <v>0.8415880018210369</v>
+        <v>0.8415880018305129</v>
       </c>
       <c r="Q4">
-        <v>12.20796310166566</v>
+        <v>12.20796310154189</v>
       </c>
       <c r="R4">
-        <v>-90.05915002988556</v>
+        <v>-90.05915002947228</v>
       </c>
       <c r="S4">
-        <v>167.7867447798104</v>
+        <v>167.7867447795301</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1779,55 +1779,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1140061092538167</v>
+        <v>0.114006109252812</v>
       </c>
       <c r="D5">
-        <v>0.1140061092538167</v>
+        <v>0.114006109252812</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.02632858353910765</v>
+        <v>0.02632858353887562</v>
       </c>
       <c r="G5">
-        <v>0.02632858353910764</v>
+        <v>0.02632858353887562</v>
       </c>
       <c r="H5">
-        <v>4.522812118725766</v>
+        <v>3.933570160969877</v>
       </c>
       <c r="I5">
-        <v>1.587622160913187</v>
+        <v>1.380280273772427</v>
       </c>
       <c r="J5">
-        <v>1.571516841080497</v>
+        <v>1.571516841130781</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985674</v>
+        <v>0.5548106983805985</v>
       </c>
       <c r="L5">
-        <v>1.571516841080487</v>
+        <v>1.57151684110335</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985962</v>
+        <v>0.5548106984276938</v>
       </c>
       <c r="N5">
-        <v>0.8227241232713802</v>
+        <v>0.8227241232777978</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.822724123271383</v>
+        <v>0.8227241232789303</v>
       </c>
       <c r="Q5">
-        <v>2.044463744672826E-13</v>
+        <v>9.932411653485673E-11</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999999925</v>
+        <v>179.999999999574</v>
       </c>
     </row>
   </sheetData>
@@ -1940,22 +1940,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9002777830291169</v>
+        <v>0.9002777830291212</v>
       </c>
       <c r="O2">
-        <v>0.8995872436685179</v>
+        <v>0.8995872436685116</v>
       </c>
       <c r="P2">
-        <v>0.8995156771822831</v>
+        <v>0.8995156771822836</v>
       </c>
       <c r="Q2">
-        <v>29.97461431204254</v>
+        <v>29.97461431204241</v>
       </c>
       <c r="R2">
-        <v>-90.05604208065985</v>
+        <v>-90.05604208065988</v>
       </c>
       <c r="S2">
-        <v>149.9973839296444</v>
+        <v>149.9973839296449</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1999,22 +1999,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7976262249650671</v>
+        <v>0.7976262249659297</v>
       </c>
       <c r="O3">
-        <v>0.337345244851981</v>
+        <v>0.3373452448502618</v>
       </c>
       <c r="P3">
-        <v>0.7973037363433458</v>
+        <v>0.7973037363479709</v>
       </c>
       <c r="Q3">
-        <v>12.20840343583034</v>
+        <v>12.2084034356383</v>
       </c>
       <c r="R3">
-        <v>-90.05604037027872</v>
+        <v>-90.0560403697408</v>
       </c>
       <c r="S3">
-        <v>167.7865824215061</v>
+        <v>167.7865824215255</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2058,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7976262224374148</v>
+        <v>0.7976262224379929</v>
       </c>
       <c r="O4">
-        <v>0.3373452828203582</v>
+        <v>0.3373452828190651</v>
       </c>
       <c r="P4">
-        <v>0.7973037469043747</v>
+        <v>0.7973037469088738</v>
       </c>
       <c r="Q4">
-        <v>12.20840487083893</v>
+        <v>12.20840487066912</v>
       </c>
       <c r="R4">
-        <v>-90.05603808977122</v>
+        <v>-90.05603808920351</v>
       </c>
       <c r="S4">
-        <v>167.7865811894647</v>
+        <v>167.7865811894686</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2084,55 +2084,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1080085409338132</v>
+        <v>0.1080085409326458</v>
       </c>
       <c r="D5">
-        <v>0.1080085409338132</v>
+        <v>0.1080085409326458</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.02494350444485348</v>
+        <v>0.02494350444458388</v>
       </c>
       <c r="G5">
-        <v>0.02494350444485348</v>
+        <v>0.02494350444458388</v>
       </c>
       <c r="H5">
-        <v>4.522801934274832</v>
+        <v>3.933559976012736</v>
       </c>
       <c r="I5">
-        <v>1.587522600685513</v>
+        <v>1.380180713276721</v>
       </c>
       <c r="J5">
-        <v>1.571506890696221</v>
+        <v>1.571506890748067</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301804</v>
+        <v>0.5547111947081454</v>
       </c>
       <c r="L5">
-        <v>1.571506890696208</v>
+        <v>1.571506890685532</v>
       </c>
       <c r="M5">
-        <v>0.5547111947302044</v>
+        <v>0.5547111947213804</v>
       </c>
       <c r="N5">
-        <v>0.7794228427583326</v>
+        <v>0.7794228427611938</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7794228427583331</v>
+        <v>0.7794228427631047</v>
       </c>
       <c r="Q5">
-        <v>1.847362039424876E-13</v>
+        <v>2.65643173196912E-11</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999999925</v>
+        <v>179.9999999997805</v>
       </c>
     </row>
   </sheetData>
@@ -2245,22 +2245,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9500530509470847</v>
+        <v>0.9500530509470877</v>
       </c>
       <c r="O2">
-        <v>0.9497600378157453</v>
+        <v>0.9497600378157427</v>
       </c>
       <c r="P2">
-        <v>0.9498269479896656</v>
+        <v>0.9498269479896673</v>
       </c>
       <c r="Q2">
-        <v>29.98979690134418</v>
+        <v>29.98979690134411</v>
       </c>
       <c r="R2">
-        <v>-90.01574914320561</v>
+        <v>-90.01574914320558</v>
       </c>
       <c r="S2">
-        <v>150.0023315106224</v>
+        <v>150.0023315106227</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2304,22 +2304,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8808915533597879</v>
+        <v>0.8808915533600858</v>
       </c>
       <c r="O3">
-        <v>0.7666473396896236</v>
+        <v>0.7666473396894532</v>
       </c>
       <c r="P3">
-        <v>0.9336241797272142</v>
+        <v>0.9336241797299624</v>
       </c>
       <c r="Q3">
-        <v>25.71535858685778</v>
+        <v>25.71535858673978</v>
       </c>
       <c r="R3">
-        <v>-85.6498900407417</v>
+        <v>-85.64989004063537</v>
       </c>
       <c r="S3">
-        <v>155.8332782869894</v>
+        <v>155.8332782869825</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2363,22 +2363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8808915561603213</v>
+        <v>0.8808915561610535</v>
       </c>
       <c r="O4">
-        <v>0.7666473535964264</v>
+        <v>0.7666473535970837</v>
       </c>
       <c r="P4">
-        <v>0.9336241827946589</v>
+        <v>0.9336241827984024</v>
       </c>
       <c r="Q4">
-        <v>25.71535900124414</v>
+        <v>25.7153590011234</v>
       </c>
       <c r="R4">
-        <v>-85.6498900836478</v>
+        <v>-85.64989008351694</v>
       </c>
       <c r="S4">
-        <v>155.8332779036259</v>
+        <v>155.8332779036027</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2389,55 +2389,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.03732736120169994</v>
+        <v>0.03732736120161708</v>
       </c>
       <c r="D5">
-        <v>0.03732736120169995</v>
+        <v>0.03732736120161709</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.008620384943629687</v>
+        <v>0.008620384943610549</v>
       </c>
       <c r="G5">
-        <v>0.008620384943629688</v>
+        <v>0.008620384943610553</v>
       </c>
       <c r="H5">
-        <v>4.522812118725766</v>
+        <v>3.933570160969877</v>
       </c>
       <c r="I5">
-        <v>1.587622160913187</v>
+        <v>1.380280273772427</v>
       </c>
       <c r="J5">
-        <v>1.571516841080497</v>
+        <v>1.571516841130781</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985674</v>
+        <v>0.5548106983805985</v>
       </c>
       <c r="L5">
-        <v>1.571516841080487</v>
+        <v>1.57151684110335</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985962</v>
+        <v>0.5548106984276938</v>
       </c>
       <c r="N5">
-        <v>0.842052741689681</v>
+        <v>0.8420527416901553</v>
       </c>
       <c r="O5">
-        <v>0.6598607459053523</v>
+        <v>0.6598607459059751</v>
       </c>
       <c r="P5">
-        <v>0.9286577670119498</v>
+        <v>0.9286577670150625</v>
       </c>
       <c r="Q5">
-        <v>22.82321092459032</v>
+        <v>22.82321092449427</v>
       </c>
       <c r="R5">
-        <v>-81.88046118251802</v>
+        <v>-81.88046118236964</v>
       </c>
       <c r="S5">
-        <v>159.4077429268681</v>
+        <v>159.4077429268419</v>
       </c>
     </row>
   </sheetData>
@@ -2550,22 +2550,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9000476025669247</v>
+        <v>0.9000476025669257</v>
       </c>
       <c r="O2">
-        <v>0.8997846179697028</v>
+        <v>0.8997846179696981</v>
       </c>
       <c r="P2">
-        <v>0.8998446688778849</v>
+        <v>0.8998446688778848</v>
       </c>
       <c r="Q2">
-        <v>29.9903337934705</v>
+        <v>29.99033379347031</v>
       </c>
       <c r="R2">
-        <v>-90.01492043928761</v>
+        <v>-90.01492043928766</v>
       </c>
       <c r="S2">
-        <v>150.0022086647021</v>
+        <v>150.0022086647023</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2609,22 +2609,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8345256958720472</v>
+        <v>0.8345256958708648</v>
       </c>
       <c r="O3">
-        <v>0.7263071262142329</v>
+        <v>0.7263071262127535</v>
       </c>
       <c r="P3">
-        <v>0.8844929730365542</v>
+        <v>0.8844929730382179</v>
       </c>
       <c r="Q3">
-        <v>25.71579867754005</v>
+        <v>25.71579867744348</v>
       </c>
       <c r="R3">
-        <v>-85.64906133703728</v>
+        <v>-85.64906133685267</v>
       </c>
       <c r="S3">
-        <v>155.8331659060389</v>
+        <v>155.8331659060782</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2668,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8345256985255942</v>
+        <v>0.8345256985244514</v>
       </c>
       <c r="O4">
-        <v>0.7263071393886883</v>
+        <v>0.7263071393872896</v>
       </c>
       <c r="P4">
-        <v>0.8844929759420576</v>
+        <v>0.8844929759439062</v>
       </c>
       <c r="Q4">
-        <v>25.71579909190197</v>
+        <v>25.71579909179949</v>
       </c>
       <c r="R4">
-        <v>-85.6490613800319</v>
+        <v>-85.64906137984232</v>
       </c>
       <c r="S4">
-        <v>155.8331655226758</v>
+        <v>155.8331655227108</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2694,55 +2694,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.03536323292340668</v>
+        <v>0.03536323292331435</v>
       </c>
       <c r="D5">
-        <v>0.03536323292340667</v>
+        <v>0.03536323292331434</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.00816678894079235</v>
+        <v>0.008166788940771028</v>
       </c>
       <c r="G5">
-        <v>0.008166788940792348</v>
+        <v>0.008166788940771027</v>
       </c>
       <c r="H5">
-        <v>4.522801934274832</v>
+        <v>3.933559976012736</v>
       </c>
       <c r="I5">
-        <v>1.587522600685513</v>
+        <v>1.380180713276721</v>
       </c>
       <c r="J5">
-        <v>1.571506890696221</v>
+        <v>1.571506890748067</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301804</v>
+        <v>0.5547111947081454</v>
       </c>
       <c r="L5">
-        <v>1.571506890696208</v>
+        <v>1.571506890685532</v>
       </c>
       <c r="M5">
-        <v>0.5547111947302044</v>
+        <v>0.5547111947213804</v>
       </c>
       <c r="N5">
-        <v>0.7977308472090685</v>
+        <v>0.7977308472080925</v>
       </c>
       <c r="O5">
-        <v>0.6251395358052024</v>
+        <v>0.6251395358045371</v>
       </c>
       <c r="P5">
-        <v>0.8797869916357326</v>
+        <v>0.8797869916377373</v>
       </c>
       <c r="Q5">
-        <v>22.82358204661208</v>
+        <v>22.82358204653189</v>
       </c>
       <c r="R5">
-        <v>-81.87963247886671</v>
+        <v>-81.87963247862992</v>
       </c>
       <c r="S5">
-        <v>159.4076470026337</v>
+        <v>159.4076470026561</v>
       </c>
     </row>
   </sheetData>
@@ -2858,22 +2858,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049405161494725</v>
+        <v>1.049355646754645</v>
       </c>
       <c r="O2">
-        <v>1.049999952316281</v>
+        <v>1.04999995231629</v>
       </c>
       <c r="P2">
-        <v>1.049892504678203</v>
+        <v>1.049883555929598</v>
       </c>
       <c r="Q2">
-        <v>29.98803578885921</v>
+        <v>29.98704043377978</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999494</v>
       </c>
       <c r="S2">
-        <v>149.9659088215051</v>
+        <v>149.9630710320541</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -2920,22 +2920,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8556805720093974</v>
+        <v>0.840406145150166</v>
       </c>
       <c r="O3">
-        <v>1.04999995231628</v>
+        <v>1.049999952325941</v>
       </c>
       <c r="P3">
-        <v>0.8561683571993326</v>
+        <v>0.8409339571406473</v>
       </c>
       <c r="Q3">
-        <v>37.81268627937582</v>
+        <v>38.62313358501228</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999981056</v>
       </c>
       <c r="S3">
-        <v>142.1452695337533</v>
+        <v>141.331877382919</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -2982,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8556805818910846</v>
+        <v>0.8404061558431307</v>
       </c>
       <c r="O4">
-        <v>1.04999995231628</v>
+        <v>1.04999995232184</v>
       </c>
       <c r="P4">
-        <v>0.8561683602599165</v>
+        <v>0.8409339603134706</v>
       </c>
       <c r="Q4">
-        <v>37.81268623691636</v>
+        <v>38.62313352779602</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999950954</v>
       </c>
       <c r="S4">
-        <v>142.1452701639597</v>
+        <v>141.3318780814931</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.1509272230408799</v>
+        <v>0.1634900929004083</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.03485514965966009</v>
+        <v>0.03775642022096955</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3026,43 +3026,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2.355702822977663</v>
+        <v>2.048805864205165</v>
       </c>
       <c r="I5">
-        <v>1.590658300946589</v>
+        <v>1.383316298483596</v>
       </c>
       <c r="J5">
-        <v>0.8185671472789061</v>
+        <v>0.8185671472875971</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806702</v>
+        <v>0.5545918926981134</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788912</v>
+        <v>0.8185671472990861</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806954</v>
+        <v>0.55459189271938</v>
       </c>
       <c r="N5">
-        <v>0.7502215279076665</v>
+        <v>0.7283370372665839</v>
       </c>
       <c r="O5">
-        <v>1.04999995231628</v>
+        <v>1.049999952327046</v>
       </c>
       <c r="P5">
-        <v>0.7507026916057175</v>
+        <v>0.728855143885991</v>
       </c>
       <c r="Q5">
-        <v>44.37366499948138</v>
+        <v>46.0814426188055</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999996692</v>
       </c>
       <c r="S5">
-        <v>135.5888119579589</v>
+        <v>133.8793507758149</v>
       </c>
       <c r="T5">
-        <v>0.1509272230408799</v>
+        <v>0.1634900929004083</v>
       </c>
     </row>
   </sheetData>
@@ -3178,22 +3178,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099347250298816</v>
+        <v>1.099292909808419</v>
       </c>
       <c r="O2">
-        <v>1.100000023841854</v>
+        <v>1.100000023841859</v>
       </c>
       <c r="P2">
-        <v>1.09988208667181</v>
+        <v>1.099872263155045</v>
       </c>
       <c r="Q2">
-        <v>29.98746742781806</v>
+        <v>29.98642491133055</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999517</v>
       </c>
       <c r="S2">
-        <v>149.9642866314647</v>
+        <v>149.9613139171964</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3240,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8964083290750448</v>
+        <v>0.88040597945049</v>
       </c>
       <c r="O3">
-        <v>1.100000023841854</v>
+        <v>1.100000023849307</v>
       </c>
       <c r="P3">
-        <v>0.8969376706513306</v>
+        <v>0.880978084791768</v>
       </c>
       <c r="Q3">
-        <v>37.81242015476329</v>
+        <v>38.6228735113525</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999981033</v>
       </c>
       <c r="S3">
-        <v>142.1440279490666</v>
+        <v>141.3305789373865</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8964083394278612</v>
+        <v>0.8804059906520355</v>
       </c>
       <c r="O4">
-        <v>1.100000023841854</v>
+        <v>1.10000002384782</v>
       </c>
       <c r="P4">
-        <v>0.8969376738570046</v>
+        <v>0.8809780881137977</v>
       </c>
       <c r="Q4">
-        <v>37.81242011234423</v>
+        <v>38.62287345418397</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999968099</v>
       </c>
       <c r="S4">
-        <v>142.1440285793225</v>
+        <v>141.3305796356603</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.1581092035367606</v>
+        <v>0.1712694318673386</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.03651375703341979</v>
+        <v>0.03955298162641024</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3346,43 +3346,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2.355710883899169</v>
+        <v>2.048813925147441</v>
       </c>
       <c r="I5">
-        <v>1.590737958073065</v>
+        <v>1.383395955583288</v>
       </c>
       <c r="J5">
-        <v>0.8185751075881735</v>
+        <v>0.8185751076119546</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339275</v>
+        <v>0.5546714956629489</v>
       </c>
       <c r="L5">
-        <v>0.8185751075881644</v>
+        <v>0.8185751076026092</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339526</v>
+        <v>0.5546714956673533</v>
       </c>
       <c r="N5">
-        <v>0.7859343212777509</v>
+        <v>0.7630084205220606</v>
       </c>
       <c r="O5">
-        <v>1.100000023841854</v>
+        <v>1.100000023850465</v>
       </c>
       <c r="P5">
-        <v>0.7864514633380699</v>
+        <v>0.7635638321480379</v>
       </c>
       <c r="Q5">
-        <v>44.37357544660215</v>
+        <v>46.0813816195169</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999599</v>
+        <v>-89.99999999996668</v>
       </c>
       <c r="S5">
-        <v>135.587929165941</v>
+        <v>133.8784995245707</v>
       </c>
       <c r="T5">
-        <v>0.1581092035367606</v>
+        <v>0.1712694318673386</v>
       </c>
     </row>
   </sheetData>
@@ -3498,22 +3498,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049884550893072</v>
+        <v>1.049882849277011</v>
       </c>
       <c r="O2">
-        <v>1.049999952316284</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="P2">
-        <v>1.049962241292751</v>
+        <v>1.049961448292776</v>
       </c>
       <c r="Q2">
-        <v>29.99874069584946</v>
+        <v>29.99873706107821</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999609</v>
       </c>
       <c r="S2">
-        <v>149.9939166887506</v>
+        <v>149.9938344520387</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3560,22 +3560,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.016612398980523</v>
+        <v>1.01620473868981</v>
       </c>
       <c r="O3">
-        <v>1.049999952316284</v>
+        <v>1.049999952318194</v>
       </c>
       <c r="P3">
-        <v>1.009729996840017</v>
+        <v>1.009119268977165</v>
       </c>
       <c r="Q3">
-        <v>31.53057351672309</v>
+        <v>31.55741343354979</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999997372</v>
       </c>
       <c r="S3">
-        <v>149.1118386525339</v>
+        <v>149.1038316494574</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3622,22 +3622,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.016612400807765</v>
+        <v>1.016204740542586</v>
       </c>
       <c r="O4">
-        <v>1.049999952316284</v>
+        <v>1.049999952317483</v>
       </c>
       <c r="P4">
-        <v>1.009729997865015</v>
+        <v>1.009119270020649</v>
       </c>
       <c r="Q4">
-        <v>31.53057350534296</v>
+        <v>31.55741342171168</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999992028</v>
       </c>
       <c r="S4">
-        <v>149.1118387391301</v>
+        <v>149.1038317372787</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02802050787318099</v>
+        <v>0.02842096997715627</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.006471059201790723</v>
+        <v>0.006563541964580974</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3666,43 +3666,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2.355702822977663</v>
+        <v>2.048805864205165</v>
       </c>
       <c r="I5">
-        <v>1.590658300946589</v>
+        <v>1.383316298483596</v>
       </c>
       <c r="J5">
-        <v>0.8185671472789061</v>
+        <v>0.8185671472875971</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806702</v>
+        <v>0.5545918926981134</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788912</v>
+        <v>0.8185671472990861</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806954</v>
+        <v>0.55459189271938</v>
       </c>
       <c r="N5">
-        <v>0.9970164450187909</v>
+        <v>0.9963782887760587</v>
       </c>
       <c r="O5">
-        <v>1.049999952316284</v>
+        <v>1.049999952318434</v>
       </c>
       <c r="P5">
-        <v>0.9857130138445218</v>
+        <v>0.9847385814790455</v>
       </c>
       <c r="Q5">
-        <v>32.49834041148088</v>
+        <v>32.54276595856023</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999629</v>
+        <v>-90.00000000000347</v>
       </c>
       <c r="S5">
-        <v>148.5481083465589</v>
+        <v>148.5344744863992</v>
       </c>
       <c r="T5">
-        <v>0.02802050787318098</v>
+        <v>0.02842096997715627</v>
       </c>
     </row>
   </sheetData>
@@ -3943,22 +3943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099873370855947</v>
+        <v>1.099871503347889</v>
       </c>
       <c r="O2">
-        <v>1.100000023841857</v>
+        <v>1.100000023841859</v>
       </c>
       <c r="P2">
-        <v>1.099958635627326</v>
+        <v>1.09995776530561</v>
       </c>
       <c r="Q2">
-        <v>29.998680771501</v>
+        <v>29.99867696477069</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999611</v>
       </c>
       <c r="S2">
-        <v>149.9936270537982</v>
+        <v>149.9935409024361</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4005,22 +4005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.065017218575355</v>
+        <v>1.06459007255594</v>
       </c>
       <c r="O3">
-        <v>1.100000023841857</v>
+        <v>1.100000023843544</v>
       </c>
       <c r="P3">
-        <v>1.057810841648753</v>
+        <v>1.05717100095338</v>
       </c>
       <c r="Q3">
-        <v>31.53052025242092</v>
+        <v>31.55736013460269</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999996308</v>
       </c>
       <c r="S3">
-        <v>149.111556202284</v>
+        <v>149.1035454466214</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.065017220489775</v>
+        <v>1.064590074496886</v>
       </c>
       <c r="O4">
-        <v>1.100000023841857</v>
+        <v>1.100000023843287</v>
       </c>
       <c r="P4">
-        <v>1.057810842722485</v>
+        <v>1.057171002046089</v>
       </c>
       <c r="Q4">
-        <v>31.53052024104956</v>
+        <v>31.55736012277469</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999994081</v>
       </c>
       <c r="S4">
-        <v>149.1115562888927</v>
+        <v>149.1035455344058</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4093,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02935461577271246</v>
+        <v>0.02977414124332754</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.006779158228350758</v>
+        <v>0.006876043487151068</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4111,43 +4111,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2.355710883899169</v>
+        <v>2.048813925147441</v>
       </c>
       <c r="I5">
-        <v>1.590737958073065</v>
+        <v>1.383395955583288</v>
       </c>
       <c r="J5">
-        <v>0.8185751075881735</v>
+        <v>0.8185751076119546</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339275</v>
+        <v>0.5546714956629489</v>
       </c>
       <c r="L5">
-        <v>0.8185751075881644</v>
+        <v>0.8185751076026092</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339526</v>
+        <v>0.5546714956673533</v>
       </c>
       <c r="N5">
-        <v>1.044488357949405</v>
+        <v>1.043819746922989</v>
       </c>
       <c r="O5">
-        <v>1.100000023841857</v>
+        <v>1.100000023843796</v>
       </c>
       <c r="P5">
-        <v>1.032650353465118</v>
+        <v>1.031629494333019</v>
       </c>
       <c r="Q5">
-        <v>32.49829104313983</v>
+        <v>32.54271662905123</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999999282</v>
       </c>
       <c r="S5">
-        <v>148.5478306633941</v>
+        <v>148.5341931664291</v>
       </c>
       <c r="T5">
-        <v>0.02935461577271246</v>
+        <v>0.02977414124332754</v>
       </c>
     </row>
   </sheetData>
@@ -4263,22 +4263,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9496845119319957</v>
+        <v>0.949658245968629</v>
       </c>
       <c r="O2">
-        <v>0.9499999880790715</v>
+        <v>0.9499999880790841</v>
       </c>
       <c r="P2">
-        <v>0.9500329587430694</v>
+        <v>0.9500357119145862</v>
       </c>
       <c r="Q2">
-        <v>29.98671883474458</v>
+        <v>29.98561251321468</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999669</v>
       </c>
       <c r="S2">
-        <v>149.9768834068171</v>
+        <v>149.9749586349279</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4325,22 +4325,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7742983739890611</v>
+        <v>0.760477027379113</v>
       </c>
       <c r="O3">
-        <v>0.9499999880790714</v>
+        <v>0.9499999880792313</v>
       </c>
       <c r="P3">
-        <v>0.7747323236489434</v>
+        <v>0.7609562080754194</v>
       </c>
       <c r="Q3">
-        <v>37.80686185065126</v>
+        <v>38.61640861247403</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999599</v>
+        <v>-90.00000000044822</v>
       </c>
       <c r="S3">
-        <v>142.1517935563774</v>
+        <v>141.3384439944849</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7742983883234159</v>
+        <v>0.7604770428335835</v>
       </c>
       <c r="O4">
-        <v>0.9499999880790714</v>
+        <v>0.9499999880797707</v>
       </c>
       <c r="P4">
-        <v>0.7747323317999008</v>
+        <v>0.7609562167077536</v>
       </c>
       <c r="Q4">
-        <v>37.80686149934937</v>
+        <v>38.61640820848137</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999601</v>
+        <v>-90.00000000059435</v>
       </c>
       <c r="S4">
-        <v>142.1517944964413</v>
+        <v>141.3384450404959</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.08099154022886543</v>
+        <v>0.08773546025650492</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.01870419530000137</v>
+        <v>0.02026163694054944</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4431,43 +4431,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>4.522812118725851</v>
+        <v>3.933570160974079</v>
       </c>
       <c r="I5">
-        <v>1.587622160913189</v>
+        <v>1.380280273863582</v>
       </c>
       <c r="J5">
-        <v>1.571516841080647</v>
+        <v>1.571516841064009</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985515</v>
+        <v>0.5548106984900895</v>
       </c>
       <c r="L5">
-        <v>1.571516841080654</v>
+        <v>1.57151684109702</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985991</v>
+        <v>0.5548106983838048</v>
       </c>
       <c r="N5">
-        <v>0.678808026569421</v>
+        <v>0.6589917494696679</v>
       </c>
       <c r="O5">
-        <v>0.9499999880790714</v>
+        <v>0.9499999880816401</v>
       </c>
       <c r="P5">
-        <v>0.6793075152473625</v>
+        <v>0.6595501214801057</v>
       </c>
       <c r="Q5">
-        <v>44.36526225934912</v>
+        <v>46.07182779675495</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999599</v>
+        <v>-90.00000000079321</v>
       </c>
       <c r="S5">
-        <v>135.5916812785048</v>
+        <v>133.8814658851767</v>
       </c>
       <c r="T5">
-        <v>0.08099154022886543</v>
+        <v>0.08773546025650492</v>
       </c>
     </row>
   </sheetData>
@@ -4583,22 +4583,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.899716835095739</v>
+        <v>0.8996932613789071</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581401</v>
+        <v>0.8999999761581396</v>
       </c>
       <c r="P2">
-        <v>0.9000295758695942</v>
+        <v>0.9000320483022675</v>
       </c>
       <c r="Q2">
-        <v>29.98741726327262</v>
+        <v>29.98636906854026</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999665</v>
       </c>
       <c r="S2">
-        <v>149.9780997491899</v>
+        <v>149.9762762255217</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4645,22 +4645,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7335563274280188</v>
+        <v>0.7204627798755721</v>
       </c>
       <c r="O3">
-        <v>0.89999997615814</v>
+        <v>0.8999999761556514</v>
       </c>
       <c r="P3">
-        <v>0.7339543289322399</v>
+        <v>0.7209030358108125</v>
       </c>
       <c r="Q3">
-        <v>37.80728131701524</v>
+        <v>38.61683493864902</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999601</v>
+        <v>-90.00000000005491</v>
       </c>
       <c r="S3">
-        <v>142.1526922772366</v>
+        <v>141.3393804778979</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4707,22 +4707,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7335563410073188</v>
+        <v>0.7204627945168764</v>
       </c>
       <c r="O4">
-        <v>0.89999997615814</v>
+        <v>0.8999999761554871</v>
       </c>
       <c r="P4">
-        <v>0.7339543366548373</v>
+        <v>0.7209030439936333</v>
       </c>
       <c r="Q4">
-        <v>37.80728096566281</v>
+        <v>38.6168345346379</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999601</v>
+        <v>-89.99999999981188</v>
       </c>
       <c r="S4">
-        <v>142.1526932172384</v>
+        <v>141.3393815242649</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4733,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.07673003009434873</v>
+        <v>0.08311921565391332</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4742,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.01772004167600932</v>
+        <v>0.01919556089908311</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4751,43 +4751,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>4.522801934274916</v>
+        <v>3.933559975952477</v>
       </c>
       <c r="I5">
-        <v>1.587522600685514</v>
+        <v>1.380180713393222</v>
       </c>
       <c r="J5">
-        <v>1.571506890696394</v>
+        <v>1.571506890669393</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301595</v>
+        <v>0.5547111948085082</v>
       </c>
       <c r="L5">
-        <v>1.571506890696374</v>
+        <v>1.571506890693625</v>
       </c>
       <c r="M5">
-        <v>0.554711194730207</v>
+        <v>0.5547111947460042</v>
       </c>
       <c r="N5">
-        <v>0.6430881891223144</v>
+        <v>0.624314521975198</v>
       </c>
       <c r="O5">
-        <v>0.89999997615814</v>
+        <v>0.8999999761579334</v>
       </c>
       <c r="P5">
-        <v>0.6435520423080709</v>
+        <v>0.6248344670690624</v>
       </c>
       <c r="Q5">
-        <v>44.36549260227559</v>
+        <v>46.07203267760097</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999599</v>
+        <v>-90.00000000039991</v>
       </c>
       <c r="S5">
-        <v>135.5923012432515</v>
+        <v>133.8820589284595</v>
       </c>
       <c r="T5">
-        <v>0.07673003009434873</v>
+        <v>0.08311921565391334</v>
       </c>
     </row>
   </sheetData>
@@ -4903,22 +4903,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9498956439606995</v>
+        <v>0.949893235424296</v>
       </c>
       <c r="O2">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790734</v>
       </c>
       <c r="P2">
-        <v>0.9499742583585884</v>
+        <v>0.9499729561511479</v>
       </c>
       <c r="Q2">
-        <v>29.9981587043088</v>
+        <v>29.99816553703928</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S2">
-        <v>149.9936292408361</v>
+        <v>149.9935068464769</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4965,22 +4965,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9115912048858601</v>
+        <v>0.9111465734357329</v>
       </c>
       <c r="O3">
-        <v>0.949999988079071</v>
+        <v>0.9499999880788087</v>
       </c>
       <c r="P3">
-        <v>0.891657214642703</v>
+        <v>0.8903441222472692</v>
       </c>
       <c r="Q3">
-        <v>32.80766227300565</v>
+        <v>32.88594799536191</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999626</v>
+        <v>-90.00000000008914</v>
       </c>
       <c r="S3">
-        <v>149.236322819813</v>
+        <v>149.2463088364919</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5027,22 +5027,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9115912085077204</v>
+        <v>0.9111465771142415</v>
       </c>
       <c r="O4">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790834</v>
       </c>
       <c r="P4">
-        <v>0.8916572182753681</v>
+        <v>0.890344125972543</v>
       </c>
       <c r="Q4">
-        <v>32.80766213118148</v>
+        <v>32.8859478485279</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999626</v>
+        <v>-90.00000000011805</v>
       </c>
       <c r="S4">
-        <v>149.2363229636874</v>
+        <v>149.2463089818476</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02288806427928413</v>
+        <v>0.02336860898735494</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5062,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.005285772107913802</v>
+        <v>0.00539674915619242</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5071,43 +5071,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>4.522812118725851</v>
+        <v>3.933570160974079</v>
       </c>
       <c r="I5">
-        <v>1.587622160913189</v>
+        <v>1.380280273863582</v>
       </c>
       <c r="J5">
-        <v>1.571516841080647</v>
+        <v>1.571516841064009</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985515</v>
+        <v>0.5548106984900895</v>
       </c>
       <c r="L5">
-        <v>1.571516841080654</v>
+        <v>1.57151684109702</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985991</v>
+        <v>0.5548106983838048</v>
       </c>
       <c r="N5">
-        <v>0.8897322598759102</v>
+        <v>0.8890860957604776</v>
       </c>
       <c r="O5">
-        <v>0.949999988079071</v>
+        <v>0.949999988079259</v>
       </c>
       <c r="P5">
-        <v>0.8567498945991119</v>
+        <v>0.8546476086130005</v>
       </c>
       <c r="Q5">
-        <v>34.60692576727709</v>
+        <v>34.73665802339898</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999626</v>
+        <v>-90.00000000018133</v>
       </c>
       <c r="S5">
-        <v>148.7325047110275</v>
+        <v>148.7479932853074</v>
       </c>
       <c r="T5">
-        <v>0.02288806427928414</v>
+        <v>0.02336860898735494</v>
       </c>
     </row>
   </sheetData>
@@ -5223,22 +5223,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.899906326098417</v>
+        <v>0.8999041643873351</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581416</v>
+        <v>0.8999999761581402</v>
       </c>
       <c r="P2">
-        <v>0.8999768838269943</v>
+        <v>0.8999757150866056</v>
       </c>
       <c r="Q2">
-        <v>29.99825556715098</v>
+        <v>29.99826203846316</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999648</v>
       </c>
       <c r="S2">
-        <v>149.9939644979276</v>
+        <v>149.993848543159</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5285,22 +5285,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8636173923875931</v>
+        <v>0.8631962599800093</v>
       </c>
       <c r="O3">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761568517</v>
       </c>
       <c r="P3">
-        <v>0.8447287809373306</v>
+        <v>0.8434848426820279</v>
       </c>
       <c r="Q3">
-        <v>32.807749667918</v>
+        <v>32.88603495465522</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999626</v>
+        <v>-89.99999999998052</v>
       </c>
       <c r="S3">
-        <v>149.2366470883845</v>
+        <v>149.2466393661994</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5347,22 +5347,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8636173958185407</v>
+        <v>0.8631962634649102</v>
       </c>
       <c r="O4">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761571471</v>
       </c>
       <c r="P4">
-        <v>0.8447287843788673</v>
+        <v>0.8434848462124623</v>
       </c>
       <c r="Q4">
-        <v>32.80774952608097</v>
+        <v>32.88603480782342</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999626</v>
+        <v>-89.99999999991903</v>
       </c>
       <c r="S4">
-        <v>149.236647232234</v>
+        <v>149.2466395116017</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02168358544583003</v>
+        <v>0.02213884616023809</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.005007609632277686</v>
+        <v>0.005112747592250344</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5391,43 +5391,43 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>4.522801934274916</v>
+        <v>3.933559975952477</v>
       </c>
       <c r="I5">
-        <v>1.587522600685514</v>
+        <v>1.380180713393222</v>
       </c>
       <c r="J5">
-        <v>1.571506890696394</v>
+        <v>1.571506890669393</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301595</v>
+        <v>0.5547111948085082</v>
       </c>
       <c r="L5">
-        <v>1.571506890696374</v>
+        <v>1.571506890693625</v>
       </c>
       <c r="M5">
-        <v>0.554711194730207</v>
+        <v>0.5547111947460042</v>
       </c>
       <c r="N5">
-        <v>0.8429086067343777</v>
+        <v>0.8422965353065947</v>
       </c>
       <c r="O5">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761572782</v>
       </c>
       <c r="P5">
-        <v>0.8116584643146362</v>
+        <v>0.8096668564352761</v>
       </c>
       <c r="Q5">
-        <v>34.60700817028153</v>
+        <v>34.73674002498053</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999626</v>
+        <v>-90.0000000000727</v>
       </c>
       <c r="S5">
-        <v>148.7328213736654</v>
+        <v>148.748316059663</v>
       </c>
       <c r="T5">
-        <v>0.02168358544583003</v>
+        <v>0.02213884616023808</v>
       </c>
     </row>
   </sheetData>
@@ -5543,22 +5543,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050093183952778</v>
+        <v>1.050066378583528</v>
       </c>
       <c r="O2">
-        <v>1.048858155155076</v>
+        <v>1.048858155155064</v>
       </c>
       <c r="P2">
-        <v>1.049082235924972</v>
+        <v>1.049077397667703</v>
       </c>
       <c r="Q2">
-        <v>29.94999094536538</v>
+        <v>29.94944994061778</v>
       </c>
       <c r="R2">
-        <v>-90.07484413230142</v>
+        <v>-90.07484413230283</v>
       </c>
       <c r="S2">
-        <v>149.9959952449163</v>
+        <v>149.9944568480232</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5605,22 +5605,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8483923461531084</v>
+        <v>0.8381568158614368</v>
       </c>
       <c r="O3">
-        <v>0.393321825478078</v>
+        <v>0.3933218254680756</v>
       </c>
       <c r="P3">
-        <v>0.8479751659851364</v>
+        <v>0.8377515582961045</v>
       </c>
       <c r="Q3">
-        <v>13.39093931012237</v>
+        <v>13.55598794216757</v>
       </c>
       <c r="R3">
-        <v>-90.07484242251006</v>
+        <v>-90.07484242292179</v>
       </c>
       <c r="S3">
-        <v>166.5776062193137</v>
+        <v>166.4090985042695</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5667,22 +5667,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8483923445715825</v>
+        <v>0.8381568147397322</v>
       </c>
       <c r="O4">
-        <v>0.3933218485379573</v>
+        <v>0.3933218485297205</v>
       </c>
       <c r="P4">
-        <v>0.8479751786721882</v>
+        <v>0.8377515712987224</v>
       </c>
       <c r="Q4">
-        <v>13.39094027609289</v>
+        <v>13.55598893105525</v>
       </c>
       <c r="R4">
-        <v>-90.0748401427859</v>
+        <v>-90.07484014395129</v>
       </c>
       <c r="S4">
-        <v>166.5776057617419</v>
+        <v>166.4090980661573</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5696,58 +5696,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.219341510502452</v>
+        <v>0.2211395284018776</v>
       </c>
       <c r="D5">
-        <v>0.2192009233252548</v>
+        <v>0.2209823313970971</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.05065475280803454</v>
+        <v>0.05106998726151847</v>
       </c>
       <c r="G5">
-        <v>0.05062228558971098</v>
+        <v>0.05103368416776719</v>
       </c>
       <c r="H5">
-        <v>2.355702822977616</v>
+        <v>2.048805864161414</v>
       </c>
       <c r="I5">
-        <v>1.590658300946586</v>
+        <v>1.383316298638611</v>
       </c>
       <c r="J5">
-        <v>0.8185671472787982</v>
+        <v>0.8185671472608929</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806581</v>
+        <v>0.5545918926652642</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788021</v>
+        <v>0.818567147237338</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806922</v>
+        <v>0.5545918926849845</v>
       </c>
       <c r="N5">
-        <v>0.7746035530760081</v>
+        <v>0.7577828414547508</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.774603553075989</v>
+        <v>0.757782841454696</v>
       </c>
       <c r="Q5">
-        <v>-0.01326884805819058</v>
+        <v>-0.01528962530022221</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9867311519327</v>
+        <v>179.9847103756725</v>
       </c>
       <c r="T5">
-        <v>0.1090050061655193</v>
+        <v>0.1226147175550796</v>
       </c>
     </row>
   </sheetData>
@@ -5863,22 +5863,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100102295403394</v>
+        <v>1.100072877611542</v>
       </c>
       <c r="O2">
-        <v>1.098746913077535</v>
+        <v>1.098746913077521</v>
       </c>
       <c r="P2">
-        <v>1.098992879472706</v>
+        <v>1.098987568022731</v>
       </c>
       <c r="Q2">
-        <v>29.94761161190063</v>
+        <v>29.94704490081214</v>
       </c>
       <c r="R2">
-        <v>-90.07840407750486</v>
+        <v>-90.07840407750621</v>
       </c>
       <c r="S2">
-        <v>149.9958073994154</v>
+        <v>149.9941957723426</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5925,22 +5925,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8887954051059372</v>
+        <v>0.8780719468708745</v>
       </c>
       <c r="O3">
-        <v>0.4120301105219057</v>
+        <v>0.4120301105118663</v>
       </c>
       <c r="P3">
-        <v>0.8883364157499625</v>
+        <v>0.877625710687</v>
       </c>
       <c r="Q3">
-        <v>13.38975927523639</v>
+        <v>13.55477019270774</v>
       </c>
       <c r="R3">
-        <v>-90.07840236732059</v>
+        <v>-90.07840236760869</v>
       </c>
       <c r="S3">
-        <v>166.5776092814928</v>
+        <v>166.4090638989015</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5987,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8887954034482386</v>
+        <v>0.8780719456954279</v>
       </c>
       <c r="O4">
-        <v>0.412030134679</v>
+        <v>0.4120301346689415</v>
       </c>
       <c r="P4">
-        <v>0.8883364290418144</v>
+        <v>0.8776257243112607</v>
       </c>
       <c r="Q4">
-        <v>13.38976024123741</v>
+        <v>13.5547711816421</v>
       </c>
       <c r="R4">
-        <v>-90.07840008707383</v>
+        <v>-90.07840008784883</v>
       </c>
       <c r="S4">
-        <v>166.5776088239396</v>
+        <v>166.4090634609864</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6016,58 +6016,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.2297767691183319</v>
+        <v>0.2316603701350904</v>
       </c>
       <c r="D5">
-        <v>0.229625676218983</v>
+        <v>0.2314918618201141</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.05306467259232181</v>
+        <v>0.05349967162043234</v>
       </c>
       <c r="G5">
-        <v>0.05302977918135716</v>
+        <v>0.05346075629144756</v>
       </c>
       <c r="H5">
-        <v>2.355710883899123</v>
+        <v>2.048813925111795</v>
       </c>
       <c r="I5">
-        <v>1.590737958073062</v>
+        <v>1.383395955732901</v>
       </c>
       <c r="J5">
-        <v>0.8185751075880874</v>
+        <v>0.818575107564779</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339436</v>
+        <v>0.5546714956012828</v>
       </c>
       <c r="L5">
-        <v>0.8185751075880753</v>
+        <v>0.8185751075552288</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339499</v>
+        <v>0.5546714956491662</v>
       </c>
       <c r="N5">
-        <v>0.8114854349559049</v>
+        <v>0.7938636853097455</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8114854349558958</v>
+        <v>0.7938636853109282</v>
       </c>
       <c r="Q5">
-        <v>-0.01361299229756682</v>
+        <v>-0.01564574051651662</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.986387007694</v>
+        <v>179.9843542605338</v>
       </c>
       <c r="T5">
-        <v>0.1141930983791527</v>
+        <v>0.1284501944978017</v>
       </c>
     </row>
   </sheetData>
@@ -6183,22 +6183,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049966382638153</v>
+        <v>1.049964880690282</v>
       </c>
       <c r="O2">
-        <v>1.049833510098441</v>
+        <v>1.049833510098439</v>
       </c>
       <c r="P2">
-        <v>1.049879450541915</v>
+        <v>1.049878775432187</v>
       </c>
       <c r="Q2">
-        <v>29.99350052693627</v>
+        <v>29.9934957383702</v>
       </c>
       <c r="R2">
-        <v>-90.00779141117509</v>
+        <v>-90.0077914111754</v>
       </c>
       <c r="S2">
-        <v>149.9991344457926</v>
+        <v>149.9990610695463</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6245,22 +6245,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.0086031930812</v>
+        <v>1.008216720555581</v>
       </c>
       <c r="O3">
-        <v>0.9704848963792059</v>
+        <v>0.970484896377185</v>
       </c>
       <c r="P3">
-        <v>1.017535493319996</v>
+        <v>1.016992848117349</v>
       </c>
       <c r="Q3">
-        <v>28.94214186930033</v>
+        <v>28.96467707374104</v>
       </c>
       <c r="R3">
-        <v>-89.21287541021805</v>
+        <v>-89.21287541026571</v>
       </c>
       <c r="S3">
-        <v>151.7062505789669</v>
+        <v>151.7000280232291</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6307,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.008603194070091</v>
+        <v>1.008216721568326</v>
       </c>
       <c r="O4">
-        <v>0.9704848995146161</v>
+        <v>0.9704848995130203</v>
       </c>
       <c r="P4">
-        <v>1.017535495188039</v>
+        <v>1.016992850001107</v>
       </c>
       <c r="Q4">
-        <v>28.94214196365434</v>
+        <v>28.96467716785306</v>
       </c>
       <c r="R4">
-        <v>-89.21287532877197</v>
+        <v>-89.212875328878</v>
       </c>
       <c r="S4">
-        <v>151.7062505598682</v>
+        <v>151.7000280050459</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6336,58 +6336,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.02946368900702673</v>
+        <v>0.02958272681114623</v>
       </c>
       <c r="D5">
-        <v>0.02893837730445435</v>
+        <v>0.02914102991452007</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.0068043476132032</v>
+        <v>0.006831838216913694</v>
       </c>
       <c r="G5">
-        <v>0.006683032070240007</v>
+        <v>0.006729832686526761</v>
       </c>
       <c r="H5">
-        <v>2.355702822977616</v>
+        <v>2.048805864161414</v>
       </c>
       <c r="I5">
-        <v>1.590658300946586</v>
+        <v>1.383316298638611</v>
       </c>
       <c r="J5">
-        <v>0.8185671472787982</v>
+        <v>0.8185671472608929</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806581</v>
+        <v>0.5545918926652642</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788021</v>
+        <v>0.818567147237338</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806922</v>
+        <v>0.5545918926849845</v>
       </c>
       <c r="N5">
-        <v>0.9839592354585591</v>
+        <v>0.9833344429195289</v>
       </c>
       <c r="O5">
-        <v>0.9229777180996085</v>
+        <v>0.9229777180969746</v>
       </c>
       <c r="P5">
-        <v>0.9985850414073588</v>
+        <v>0.997714088349071</v>
       </c>
       <c r="Q5">
-        <v>28.26903173980342</v>
+        <v>28.30557918134636</v>
       </c>
       <c r="R5">
-        <v>-88.67038236123848</v>
+        <v>-88.67038236126554</v>
       </c>
       <c r="S5">
-        <v>152.7830380982342</v>
+        <v>152.7738735612169</v>
       </c>
       <c r="T5">
-        <v>0.02617319320691305</v>
+        <v>0.02688184221626237</v>
       </c>
     </row>
   </sheetData>
@@ -6503,22 +6503,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099963180655161</v>
+        <v>1.099961532279688</v>
       </c>
       <c r="O2">
-        <v>1.099817353423622</v>
+        <v>1.099817353423621</v>
       </c>
       <c r="P2">
-        <v>1.099867773364175</v>
+        <v>1.099867032420956</v>
       </c>
       <c r="Q2">
-        <v>29.99319107877399</v>
+        <v>29.99318606277595</v>
       </c>
       <c r="R2">
-        <v>-90.00816236914068</v>
+        <v>-90.00816236914098</v>
       </c>
       <c r="S2">
-        <v>149.9990932713999</v>
+        <v>149.999016402051</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6565,22 +6565,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.056630588978267</v>
+        <v>1.056225646094768</v>
       </c>
       <c r="O3">
-        <v>1.016690856223135</v>
+        <v>1.016690856221457</v>
       </c>
       <c r="P3">
-        <v>1.065984051748929</v>
+        <v>1.065415536756872</v>
       </c>
       <c r="Q3">
-        <v>28.94184165499475</v>
+        <v>28.96437642524356</v>
       </c>
       <c r="R3">
-        <v>-89.21324636811474</v>
+        <v>-89.21324636817151</v>
       </c>
       <c r="S3">
-        <v>151.7062148753855</v>
+        <v>151.6999891540817</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6627,22 +6627,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.056630590014157</v>
+        <v>1.056225647155871</v>
       </c>
       <c r="O4">
-        <v>1.016690859507956</v>
+        <v>1.01669085950638</v>
       </c>
       <c r="P4">
-        <v>1.065984053706107</v>
+        <v>1.065415538730832</v>
       </c>
       <c r="Q4">
-        <v>28.94184174936154</v>
+        <v>28.96437651936873</v>
       </c>
       <c r="R4">
-        <v>-89.21324628664352</v>
+        <v>-89.21324628673484</v>
       </c>
       <c r="S4">
-        <v>151.7062148562952</v>
+        <v>151.6999891359443</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6656,58 +6656,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.03086650658275633</v>
+        <v>0.03099120949196726</v>
       </c>
       <c r="D5">
-        <v>0.03031616628312807</v>
+        <v>0.0305284680310871</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.007128314460019251</v>
+        <v>0.007157113363729052</v>
       </c>
       <c r="G5">
-        <v>0.007001218810070868</v>
+        <v>0.007050247799334886</v>
       </c>
       <c r="H5">
-        <v>2.355710883899123</v>
+        <v>2.048813925111795</v>
       </c>
       <c r="I5">
-        <v>1.590737958073062</v>
+        <v>1.383395955732901</v>
       </c>
       <c r="J5">
-        <v>0.8185751075880874</v>
+        <v>0.818575107564779</v>
       </c>
       <c r="K5">
-        <v>0.5546714956339436</v>
+        <v>0.5546714956012828</v>
       </c>
       <c r="L5">
-        <v>0.8185751075880753</v>
+        <v>0.8185751075552288</v>
       </c>
       <c r="M5">
-        <v>0.5546714956339499</v>
+        <v>0.5546714956491662</v>
       </c>
       <c r="N5">
-        <v>1.03081327021884</v>
+        <v>1.03015866368835</v>
       </c>
       <c r="O5">
-        <v>0.9669218037196279</v>
+        <v>0.9669218037172662</v>
       </c>
       <c r="P5">
-        <v>1.046131452205713</v>
+        <v>1.04521899831217</v>
       </c>
       <c r="Q5">
-        <v>28.26873765469647</v>
+        <v>28.30528453363673</v>
       </c>
       <c r="R5">
-        <v>-88.67075331912008</v>
+        <v>-88.67075331915616</v>
       </c>
       <c r="S5">
-        <v>152.7830054445417</v>
+        <v>152.7738379522614</v>
       </c>
       <c r="T5">
-        <v>0.02741936114991888</v>
+        <v>0.02816174505622352</v>
       </c>
     </row>
   </sheetData>
@@ -6823,22 +6823,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9501956522376941</v>
+        <v>0.950181441589941</v>
       </c>
       <c r="O2">
-        <v>0.9495401076448402</v>
+        <v>0.9495401076448373</v>
       </c>
       <c r="P2">
-        <v>0.9494723533687091</v>
+        <v>0.9494738578099898</v>
       </c>
       <c r="Q2">
-        <v>29.96840480291807</v>
+        <v>29.9678048990147</v>
       </c>
       <c r="R2">
-        <v>-90.05915402191762</v>
+        <v>-90.05915402191749</v>
       </c>
       <c r="S2">
-        <v>149.9888890299318</v>
+        <v>149.9878461693023</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6885,22 +6885,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7676272895606568</v>
+        <v>0.7583707044686586</v>
       </c>
       <c r="O3">
-        <v>0.356077570424658</v>
+        <v>0.3560775704250813</v>
       </c>
       <c r="P3">
-        <v>0.7673455823868884</v>
+        <v>0.7581022471652002</v>
       </c>
       <c r="Q3">
-        <v>13.39839820029231</v>
+        <v>13.56304486382595</v>
       </c>
       <c r="R3">
-        <v>-90.05915231104666</v>
+        <v>-90.05915231073728</v>
       </c>
       <c r="S3">
-        <v>166.5714821203922</v>
+        <v>166.4026290660054</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7676272927516076</v>
+        <v>0.7583707083996957</v>
       </c>
       <c r="O4">
-        <v>0.3560776105017739</v>
+        <v>0.3560776105040876</v>
       </c>
       <c r="P4">
-        <v>0.7673455984925113</v>
+        <v>0.7581022638873584</v>
       </c>
       <c r="Q4">
-        <v>13.39839982135422</v>
+        <v>13.56304650940336</v>
       </c>
       <c r="R4">
-        <v>-90.05915002988588</v>
+        <v>-90.05915002922673</v>
       </c>
       <c r="S4">
-        <v>166.5714810084464</v>
+        <v>166.4026279722056</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6976,58 +6976,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1177403189751624</v>
+        <v>0.1187074245730195</v>
       </c>
       <c r="D5">
-        <v>0.1176537455824868</v>
+        <v>0.1186069274300428</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.02719096234708988</v>
+        <v>0.02741430582132099</v>
       </c>
       <c r="G5">
-        <v>0.02717096907816558</v>
+        <v>0.027391096999955</v>
       </c>
       <c r="H5">
-        <v>4.522812118725766</v>
+        <v>3.933570160969877</v>
       </c>
       <c r="I5">
-        <v>1.587622160913187</v>
+        <v>1.380280273772427</v>
       </c>
       <c r="J5">
-        <v>1.571516841080497</v>
+        <v>1.571516841130781</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985674</v>
+        <v>0.5548106983805985</v>
       </c>
       <c r="L5">
-        <v>1.571516841080487</v>
+        <v>1.57151684110335</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985962</v>
+        <v>0.5548106984276938</v>
       </c>
       <c r="N5">
-        <v>0.700881619378979</v>
+        <v>0.6856657597875194</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7008816193789809</v>
+        <v>0.6856657597877989</v>
       </c>
       <c r="Q5">
-        <v>-0.01522072276476922</v>
+        <v>-0.01820812665637319</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9847792772273</v>
+        <v>179.9817918729927</v>
       </c>
       <c r="T5">
-        <v>0.0584876169385497</v>
+        <v>0.06579164064336127</v>
       </c>
     </row>
   </sheetData>
@@ -7268,22 +7268,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9001756085815555</v>
+        <v>0.9001628543162312</v>
       </c>
       <c r="O2">
-        <v>0.8995872436685173</v>
+        <v>0.8995872436685155</v>
       </c>
       <c r="P2">
-        <v>0.8995264125181158</v>
+        <v>0.8995277634275146</v>
       </c>
       <c r="Q2">
-        <v>29.9700674884338</v>
+        <v>29.96949912093956</v>
       </c>
       <c r="R2">
         <v>-90.05604208065985</v>
       </c>
       <c r="S2">
-        <v>149.9894723102583</v>
+        <v>149.9884843455724</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7330,22 +7330,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7272210466395611</v>
+        <v>0.7184519009863558</v>
       </c>
       <c r="O3">
-        <v>0.3373452448519825</v>
+        <v>0.3373452448516132</v>
       </c>
       <c r="P3">
-        <v>0.7269698804085455</v>
+        <v>0.7182130987878669</v>
       </c>
       <c r="Q3">
-        <v>13.39920426312981</v>
+        <v>13.56388392047129</v>
       </c>
       <c r="R3">
-        <v>-90.05604037027908</v>
+        <v>-90.05604037012135</v>
       </c>
       <c r="S3">
-        <v>166.5717052845488</v>
+        <v>166.4028852058211</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7392,22 +7392,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7272210496634235</v>
+        <v>0.7184519047108053</v>
       </c>
       <c r="O4">
-        <v>0.3373452828203597</v>
+        <v>0.3373452828206198</v>
       </c>
       <c r="P4">
-        <v>0.7269698956657791</v>
+        <v>0.7182131146238827</v>
       </c>
       <c r="Q4">
-        <v>13.39920588415361</v>
+        <v>13.56388556594059</v>
       </c>
       <c r="R4">
-        <v>-90.05603808977158</v>
+        <v>-90.05603809012351</v>
       </c>
       <c r="S4">
-        <v>166.5717041725794</v>
+        <v>166.4028841119109</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7421,58 +7421,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1115453960600409</v>
+        <v>0.1124616086540162</v>
       </c>
       <c r="D5">
-        <v>0.1114649974536857</v>
+        <v>0.1123680256886151</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.02576030616070968</v>
+        <v>0.02597189639896924</v>
       </c>
       <c r="G5">
-        <v>0.02574173889762435</v>
+        <v>0.02595028433854086</v>
       </c>
       <c r="H5">
-        <v>4.522801934274832</v>
+        <v>3.933559976012736</v>
       </c>
       <c r="I5">
-        <v>1.587522600685513</v>
+        <v>1.380180713276721</v>
       </c>
       <c r="J5">
-        <v>1.571506890696221</v>
+        <v>1.571506890748067</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301804</v>
+        <v>0.5547111947081454</v>
       </c>
       <c r="L5">
-        <v>1.571506890696208</v>
+        <v>1.571506890685532</v>
       </c>
       <c r="M5">
-        <v>0.5547111947302044</v>
+        <v>0.5547111947213804</v>
       </c>
       <c r="N5">
-        <v>0.6639947329831875</v>
+        <v>0.6495797284134666</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6639947329831869</v>
+        <v>0.6495797284138614</v>
       </c>
       <c r="Q5">
-        <v>-0.01491996965678114</v>
+        <v>-0.01789686020733552</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9850800303353</v>
+        <v>179.9821031394388</v>
       </c>
       <c r="T5">
-        <v>0.05540994875000901</v>
+        <v>0.06232971666015968</v>
       </c>
     </row>
   </sheetData>
@@ -7588,22 +7588,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499786983413349</v>
+        <v>0.9499766834418668</v>
       </c>
       <c r="O2">
-        <v>0.9498493127643457</v>
+        <v>0.9498493127643414</v>
       </c>
       <c r="P2">
-        <v>0.9498889823312781</v>
+        <v>0.9498879948157185</v>
       </c>
       <c r="Q2">
-        <v>29.99294040496339</v>
+        <v>29.99293900422605</v>
       </c>
       <c r="R2">
-        <v>-90.00880286124381</v>
+        <v>-90.00880286124388</v>
       </c>
       <c r="S2">
-        <v>149.9988275796437</v>
+        <v>149.9987216323868</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7650,22 +7650,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8871046165909749</v>
+        <v>0.8866047679185449</v>
       </c>
       <c r="O3">
-        <v>0.8433958146138302</v>
+        <v>0.8433958146123072</v>
       </c>
       <c r="P3">
-        <v>0.9158407749664418</v>
+        <v>0.9147447941826231</v>
       </c>
       <c r="Q3">
-        <v>28.9179203513257</v>
+        <v>28.98158774561795</v>
       </c>
       <c r="R3">
-        <v>-87.2332187851549</v>
+        <v>-87.2332187850232</v>
       </c>
       <c r="S3">
-        <v>153.1638486263833</v>
+        <v>153.172666201144</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8871046203998701</v>
+        <v>0.886604771787903</v>
       </c>
       <c r="O4">
-        <v>0.8433958228262468</v>
+        <v>0.8433958228248248</v>
       </c>
       <c r="P4">
-        <v>0.9158407784207305</v>
+        <v>0.9147447977144948</v>
       </c>
       <c r="Q4">
-        <v>28.91792052581293</v>
+        <v>28.98158791639301</v>
       </c>
       <c r="R4">
-        <v>-87.23321882522001</v>
+        <v>-87.23321882505742</v>
       </c>
       <c r="S4">
-        <v>153.1638484535316</v>
+        <v>153.1726660291112</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7741,58 +7741,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.0250466556602136</v>
+        <v>0.02513079952174391</v>
       </c>
       <c r="D5">
-        <v>0.02372523360439263</v>
+        <v>0.0239960487520811</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.005784277441282125</v>
+        <v>0.005803709634013758</v>
       </c>
       <c r="G5">
-        <v>0.005479108084878208</v>
+        <v>0.005541650165177585</v>
       </c>
       <c r="H5">
-        <v>4.522812118725766</v>
+        <v>3.933570160969877</v>
       </c>
       <c r="I5">
-        <v>1.587622160913187</v>
+        <v>1.380280273772427</v>
       </c>
       <c r="J5">
-        <v>1.571516841080497</v>
+        <v>1.571516841130781</v>
       </c>
       <c r="K5">
-        <v>0.5548106983985674</v>
+        <v>0.5548106983805985</v>
       </c>
       <c r="L5">
-        <v>1.571516841080487</v>
+        <v>1.57151684110335</v>
       </c>
       <c r="M5">
-        <v>0.5548106983985962</v>
+        <v>0.5548106984276938</v>
       </c>
       <c r="N5">
-        <v>0.8495477962360013</v>
+        <v>0.8487300366376871</v>
       </c>
       <c r="O5">
-        <v>0.7806802297402592</v>
+        <v>0.7806802297387493</v>
       </c>
       <c r="P5">
-        <v>0.8968334030023999</v>
+        <v>0.8950895304455719</v>
       </c>
       <c r="Q5">
-        <v>28.19668005140205</v>
+        <v>28.30240851207425</v>
       </c>
       <c r="R5">
-        <v>-85.20736638980102</v>
+        <v>-85.20736638960916</v>
       </c>
       <c r="S5">
-        <v>155.1745946963374</v>
+        <v>155.1930059827621</v>
       </c>
       <c r="T5">
-        <v>0.02074044582506535</v>
+        <v>0.0215512791955816</v>
       </c>
     </row>
   </sheetData>
@@ -7908,22 +7908,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999808688911581</v>
+        <v>0.899979060481638</v>
       </c>
       <c r="O2">
-        <v>0.8998647434222096</v>
+        <v>0.8998647434222082</v>
       </c>
       <c r="P2">
-        <v>0.8999003470049651</v>
+        <v>0.8998994607121276</v>
       </c>
       <c r="Q2">
-        <v>29.99331190940437</v>
+        <v>29.99331058147908</v>
       </c>
       <c r="R2">
-        <v>-90.00833962237523</v>
+        <v>-90.00833962237525</v>
       </c>
       <c r="S2">
-        <v>149.9988892384323</v>
+        <v>149.9987888659221</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7970,22 +7970,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8404155364617589</v>
+        <v>0.8399420823855824</v>
       </c>
       <c r="O3">
-        <v>0.7990132204352338</v>
+        <v>0.7990132204347701</v>
       </c>
       <c r="P3">
-        <v>0.8676435827350991</v>
+        <v>0.8666053239228722</v>
       </c>
       <c r="Q3">
-        <v>28.91827587669723</v>
+        <v>28.98194398905862</v>
       </c>
       <c r="R3">
-        <v>-87.23275554641177</v>
+        <v>-87.23275554636867</v>
       </c>
       <c r="S3">
-        <v>153.163905550327</v>
+        <v>153.1727278796377</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8032,22 +8032,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8404155400702821</v>
+        <v>0.839942086051107</v>
       </c>
       <c r="O4">
-        <v>0.7990132282151163</v>
+        <v>0.7990132282145499</v>
       </c>
       <c r="P4">
-        <v>0.8676435860072655</v>
+        <v>0.8666053272673522</v>
       </c>
       <c r="Q4">
-        <v>28.91827605115775</v>
+        <v>28.98194415978555</v>
       </c>
       <c r="R4">
-        <v>-87.23275558652369</v>
+        <v>-87.23275558654791</v>
       </c>
       <c r="S4">
-        <v>153.1639053774645</v>
+        <v>153.1727277075339</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8061,58 +8061,58 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.02372858983132188</v>
+        <v>0.02380830834110068</v>
       </c>
       <c r="D5">
-        <v>0.02247672664177442</v>
+        <v>0.02273328949295331</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.005479883172298183</v>
+        <v>0.00549829337380459</v>
       </c>
       <c r="G5">
-        <v>0.005190777748200652</v>
+        <v>0.005250028401560431</v>
       </c>
       <c r="H5">
-        <v>4.522801934274832</v>
+        <v>3.933559976012736</v>
       </c>
       <c r="I5">
-        <v>1.587522600685513</v>
+        <v>1.380180713276721</v>
       </c>
       <c r="J5">
-        <v>1.571506890696221</v>
+        <v>1.571506890748067</v>
       </c>
       <c r="K5">
-        <v>0.5547111947301804</v>
+        <v>0.5547111947081454</v>
       </c>
       <c r="L5">
-        <v>1.571506890696208</v>
+        <v>1.571506890685532</v>
       </c>
       <c r="M5">
-        <v>0.5547111947302044</v>
+        <v>0.5547111947213804</v>
       </c>
       <c r="N5">
-        <v>0.8048351480855921</v>
+        <v>0.8040605065676654</v>
       </c>
       <c r="O5">
-        <v>0.7395979606328986</v>
+        <v>0.7395979606324838</v>
       </c>
       <c r="P5">
-        <v>0.8496362626807746</v>
+        <v>0.8479842047961805</v>
       </c>
       <c r="Q5">
-        <v>28.1970243688389</v>
+        <v>28.30275398941421</v>
       </c>
       <c r="R5">
-        <v>-85.206903151086</v>
+        <v>-85.20690315098938</v>
       </c>
       <c r="S5">
-        <v>155.1746500239439</v>
+        <v>155.193065557254</v>
       </c>
       <c r="T5">
-        <v>0.01964896742494032</v>
+        <v>0.02041713700592591</v>
       </c>
     </row>
   </sheetData>
@@ -8850,22 +8850,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050307883088287</v>
+        <v>1.050307883088289</v>
       </c>
       <c r="O2">
-        <v>1.048858155155077</v>
+        <v>1.04885815515507</v>
       </c>
       <c r="P2">
-        <v>1.049121020348275</v>
+        <v>1.049121020348254</v>
       </c>
       <c r="Q2">
-        <v>29.95432274588553</v>
+        <v>29.95432274588552</v>
       </c>
       <c r="R2">
-        <v>-90.07484413230142</v>
+        <v>-90.07484413230257</v>
       </c>
       <c r="S2">
-        <v>150.008316244496</v>
+        <v>150.0083162444958</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -8909,22 +8909,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9306006817958639</v>
+        <v>0.9306006817964569</v>
       </c>
       <c r="O3">
-        <v>0.3933218254780761</v>
+        <v>0.3933218254705555</v>
       </c>
       <c r="P3">
-        <v>0.9300985163068081</v>
+        <v>0.9300985163028639</v>
       </c>
       <c r="Q3">
-        <v>12.20010993843269</v>
+        <v>12.20010993840062</v>
       </c>
       <c r="R3">
-        <v>-90.07484242250951</v>
+        <v>-90.07484242297423</v>
       </c>
       <c r="S3">
-        <v>167.7932016787505</v>
+        <v>167.793201679148</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -8968,22 +8968,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9306006766011731</v>
+        <v>0.9306006766019708</v>
       </c>
       <c r="O4">
-        <v>0.3933218485379555</v>
+        <v>0.39332184853027</v>
       </c>
       <c r="P4">
-        <v>0.9300985263801065</v>
+        <v>0.9300985263747595</v>
       </c>
       <c r="Q4">
-        <v>12.20011073451123</v>
+        <v>12.20011073444912</v>
       </c>
       <c r="R4">
-        <v>-90.07484014278535</v>
+        <v>-90.07484014351171</v>
       </c>
       <c r="S4">
-        <v>167.7932010856526</v>
+        <v>167.7932010860147</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -8994,55 +8994,55 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.2123896152493923</v>
+        <v>0.2123896152494208</v>
       </c>
       <c r="D5">
-        <v>0.2123896152493924</v>
+        <v>0.2123896152494208</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.04904928134581833</v>
+        <v>0.0490492813458249</v>
       </c>
       <c r="G5">
-        <v>0.04904928134581834</v>
+        <v>0.0490492813458249</v>
       </c>
       <c r="H5">
-        <v>2.355702822977616</v>
+        <v>2.048805864161414</v>
       </c>
       <c r="I5">
-        <v>1.590658300946586</v>
+        <v>1.383316298638611</v>
       </c>
       <c r="J5">
-        <v>0.8185671472787982</v>
+        <v>0.8185671472608929</v>
       </c>
       <c r="K5">
-        <v>0.5545918926806581</v>
+        <v>0.5545918926652642</v>
       </c>
       <c r="L5">
-        <v>0.8185671472788021</v>
+        <v>0.818567147237338</v>
       </c>
       <c r="M5">
-        <v>0.5545918926806922</v>
+        <v>0.5545918926849845</v>
       </c>
       <c r="N5">
-        <v>0.9093266326783732</v>
+        <v>0.9093266326787066</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9093266326783572</v>
+        <v>0.9093266326737094</v>
       </c>
       <c r="Q5">
-        <v>6.508435779572864E-13</v>
+        <v>-5.574191769356867E-11</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999999921</v>
+        <v>-179.9999999993694</v>
       </c>
     </row>
   </sheetData>
